--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_121_R13.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_121_R13.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>8.367699999999999</v>
+        <v>7.7415</v>
       </c>
       <c r="E2" t="n">
-        <v>6.0584</v>
+        <v>5.2642</v>
       </c>
       <c r="F2" t="n">
-        <v>2.3093</v>
+        <v>2.4773</v>
       </c>
       <c r="G2" t="n">
         <v>4.9954</v>
@@ -610,13 +610,13 @@
         <v>1.8556</v>
       </c>
       <c r="S2" t="n">
-        <v>1.1224</v>
+        <v>0.4962</v>
       </c>
       <c r="T2" t="n">
-        <v>1.5454</v>
+        <v>0.7512</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.423</v>
+        <v>-0.255</v>
       </c>
       <c r="V2" t="n">
         <v>0.3943</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.6721</v>
+        <v>4.5616</v>
       </c>
       <c r="E3" t="n">
-        <v>5.5732</v>
+        <v>5.53</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.9011</v>
+        <v>-0.9683</v>
       </c>
       <c r="G3" t="n">
         <v>3.9929</v>
@@ -688,13 +688,13 @@
         <v>1.6237</v>
       </c>
       <c r="S3" t="n">
-        <v>0.478</v>
+        <v>0.3675</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.1019</v>
+        <v>-0.1452</v>
       </c>
       <c r="U3" t="n">
-        <v>0.5799</v>
+        <v>0.5127</v>
       </c>
       <c r="V3" t="n">
         <v>3.2166</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.5615</v>
+        <v>2.5525</v>
       </c>
       <c r="E4" t="n">
-        <v>3.1225</v>
+        <v>3.3152</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.5610000000000001</v>
+        <v>-0.7627</v>
       </c>
       <c r="G4" t="n">
         <v>0.851</v>
@@ -766,13 +766,13 @@
         <v>2.3195</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.1581</v>
+        <v>-0.1672</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.2513</v>
+        <v>-0.0587</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0931</v>
+        <v>-0.1085</v>
       </c>
       <c r="V4" t="n">
         <v>0.7089</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>M. KABENGELE</t>
+          <t>T. ARMSTRONG</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.8762</v>
+        <v>0.7581</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.3612</v>
+        <v>0.1348</v>
       </c>
       <c r="F5" t="n">
-        <v>1.2374</v>
+        <v>0.6232</v>
       </c>
       <c r="G5" t="n">
-        <v>-3.704</v>
+        <v>1.734</v>
       </c>
       <c r="H5" t="n">
-        <v>-2.185</v>
+        <v>0.9376</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.5191</v>
+        <v>0.7964</v>
       </c>
       <c r="J5" t="n">
-        <v>-1.8601</v>
+        <v>1.4123</v>
       </c>
       <c r="K5" t="n">
-        <v>-2.2883</v>
+        <v>0.8234</v>
       </c>
       <c r="L5" t="n">
-        <v>0.4282</v>
+        <v>0.5889</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.8439</v>
+        <v>0.3217</v>
       </c>
       <c r="N5" t="n">
-        <v>0.1034</v>
+        <v>0.1141</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.9473</v>
+        <v>0.2075</v>
       </c>
       <c r="P5" t="n">
-        <v>-2.5515</v>
+        <v>-0.4639</v>
       </c>
       <c r="Q5" t="n">
-        <v>-3.4793</v>
+        <v>-1.1598</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9278</v>
+        <v>0.6959</v>
       </c>
       <c r="S5" t="n">
-        <v>2.8739</v>
+        <v>-0.512</v>
       </c>
       <c r="T5" t="n">
-        <v>1.7616</v>
+        <v>-0.1177</v>
       </c>
       <c r="U5" t="n">
-        <v>1.1123</v>
+        <v>-0.3943</v>
       </c>
       <c r="V5" t="n">
-        <v>4.2578</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>3.2166</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>1.0412</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8205</v>
+        <v>0.6942</v>
       </c>
       <c r="E6" t="n">
-        <v>0.3313</v>
+        <v>0.6419</v>
       </c>
       <c r="F6" t="n">
-        <v>0.4891</v>
+        <v>0.0523</v>
       </c>
       <c r="G6" t="n">
         <v>2.4173</v>
@@ -922,13 +922,13 @@
         <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.4371</v>
+        <v>-0.5634</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.2829</v>
+        <v>0.0277</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.1542</v>
+        <v>-0.5911</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>T. ARMSTRONG</t>
+          <t>M. KABENGELE</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.3199</v>
+        <v>-0.6827</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.337</v>
+        <v>-1.584</v>
       </c>
       <c r="F7" t="n">
-        <v>0.6569</v>
+        <v>0.9013</v>
       </c>
       <c r="G7" t="n">
-        <v>1.734</v>
+        <v>-3.704</v>
       </c>
       <c r="H7" t="n">
-        <v>0.9376</v>
+        <v>-2.185</v>
       </c>
       <c r="I7" t="n">
-        <v>0.7964</v>
+        <v>-1.5191</v>
       </c>
       <c r="J7" t="n">
-        <v>1.4123</v>
+        <v>-1.8601</v>
       </c>
       <c r="K7" t="n">
-        <v>0.8234</v>
+        <v>-2.2883</v>
       </c>
       <c r="L7" t="n">
-        <v>0.5889</v>
+        <v>0.4282</v>
       </c>
       <c r="M7" t="n">
-        <v>0.3217</v>
+        <v>-1.8439</v>
       </c>
       <c r="N7" t="n">
-        <v>0.1141</v>
+        <v>0.1034</v>
       </c>
       <c r="O7" t="n">
-        <v>0.2075</v>
+        <v>-1.9473</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.4639</v>
+        <v>-2.5515</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.1598</v>
+        <v>-3.4793</v>
       </c>
       <c r="R7" t="n">
-        <v>0.6959</v>
+        <v>0.9278</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.9502</v>
+        <v>1.315</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.5895</v>
+        <v>0.5387999999999999</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.3607</v>
+        <v>0.7762</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>4.2578</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>3.2166</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1.0412</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. ABASS</t>
+          <t>K. PREPELIC</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.4624</v>
+        <v>-1.6717</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.9388</v>
+        <v>-2.6825</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.5236</v>
+        <v>1.0108</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.7379</v>
+        <v>0.8186</v>
       </c>
       <c r="H8" t="n">
-        <v>0.6243</v>
+        <v>1.6653</v>
       </c>
       <c r="I8" t="n">
-        <v>-2.3622</v>
+        <v>-0.8466</v>
       </c>
       <c r="J8" t="n">
-        <v>0.1811</v>
+        <v>-0.4501</v>
       </c>
       <c r="K8" t="n">
-        <v>0.8571</v>
+        <v>0.39</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.6758999999999999</v>
+        <v>-0.8401</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.919</v>
+        <v>1.2687</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.2327</v>
+        <v>1.2753</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.6862</v>
+        <v>-0.0065</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.4639</v>
+        <v>-0.6959</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.1598</v>
+        <v>-2.3195</v>
       </c>
       <c r="R8" t="n">
-        <v>0.6959</v>
+        <v>1.6237</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.4024</v>
+        <v>-0.8641</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.1019</v>
+        <v>-0.0547</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.3005</v>
+        <v>-0.8094</v>
       </c>
       <c r="V8" t="n">
-        <v>0.1418</v>
+        <v>-0.9304</v>
       </c>
       <c r="W8" t="n">
         <v>0.1418</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>K. PREPELIC</t>
+          <t>A. ABASS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.8148</v>
+        <v>-2.4294</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.6576</v>
+        <v>-1.1747</v>
       </c>
       <c r="F9" t="n">
-        <v>0.8428</v>
+        <v>-1.2548</v>
       </c>
       <c r="G9" t="n">
-        <v>0.8186</v>
+        <v>-1.7379</v>
       </c>
       <c r="H9" t="n">
-        <v>1.6653</v>
+        <v>0.6243</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.8466</v>
+        <v>-2.3622</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.4501</v>
+        <v>0.1811</v>
       </c>
       <c r="K9" t="n">
-        <v>0.39</v>
+        <v>0.8571</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.8401</v>
+        <v>-0.6758999999999999</v>
       </c>
       <c r="M9" t="n">
-        <v>1.2687</v>
+        <v>-1.919</v>
       </c>
       <c r="N9" t="n">
-        <v>1.2753</v>
+        <v>-0.2327</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.0065</v>
+        <v>-1.6862</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.6959</v>
+        <v>-0.4639</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.3195</v>
+        <v>-1.1598</v>
       </c>
       <c r="R9" t="n">
-        <v>1.6237</v>
+        <v>0.6959</v>
       </c>
       <c r="S9" t="n">
-        <v>-2.0072</v>
+        <v>-0.3695</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.0297</v>
+        <v>-0.3378</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.9774</v>
+        <v>-0.0316</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.9304</v>
+        <v>0.1418</v>
       </c>
       <c r="W9" t="n">
         <v>0.1418</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.0722</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-5.2543</v>
+        <v>-4.7757</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.5066</v>
+        <v>-2.196</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.7477</v>
+        <v>-2.5797</v>
       </c>
       <c r="G10" t="n">
         <v>-1.4489</v>
@@ -1234,13 +1234,13 @@
         <v>0.4639</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.9651</v>
+        <v>-0.4865</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.4481</v>
+        <v>-0.1375</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.5171</v>
+        <v>-0.349</v>
       </c>
       <c r="V10" t="n">
         <v>-2.1444</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-7.0651</v>
+        <v>-5.9803</v>
       </c>
       <c r="E11" t="n">
-        <v>-6.221</v>
+        <v>-5.4386</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.8441</v>
+        <v>-0.5416</v>
       </c>
       <c r="G11" t="n">
         <v>-5.1484</v>
@@ -1312,13 +1312,13 @@
         <v>1.3917</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.9527</v>
+        <v>-0.8678</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.187</v>
+        <v>-0.4046</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.7657</v>
+        <v>-0.4632</v>
       </c>
       <c r="V11" t="n">
         <v>-1.3558</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>0.02129999999999832</v>
+        <v>0.7681000000000013</v>
       </c>
       <c r="E12" t="n">
-        <v>1.063199999999998</v>
+        <v>1.810299999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.042</v>
+        <v>-1.0422</v>
       </c>
       <c r="G12" t="n">
         <v>2.77</v>
@@ -1363,10 +1363,10 @@
         <v>-3.412999999999999</v>
       </c>
       <c r="J12" t="n">
-        <v>5.056900000000002</v>
+        <v>5.0569</v>
       </c>
       <c r="K12" t="n">
-        <v>1.595</v>
+        <v>1.594999999999999</v>
       </c>
       <c r="L12" t="n">
         <v>3.462</v>
@@ -1381,7 +1381,7 @@
         <v>-6.8748</v>
       </c>
       <c r="P12" t="n">
-        <v>-4.6392</v>
+        <v>-4.639199999999999</v>
       </c>
       <c r="Q12" t="n">
         <v>-16.2368</v>
@@ -1390,13 +1390,13 @@
         <v>11.5977</v>
       </c>
       <c r="S12" t="n">
-        <v>-2.3985</v>
+        <v>-1.6518</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.6853000000000002</v>
+        <v>0.06149999999999989</v>
       </c>
       <c r="U12" t="n">
-        <v>-1.7133</v>
+        <v>-1.7132</v>
       </c>
       <c r="V12" t="n">
         <v>4.2888</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>8.5783</v>
+        <v>7.1185</v>
       </c>
       <c r="E13" t="n">
-        <v>7.4059</v>
+        <v>5.9904</v>
       </c>
       <c r="F13" t="n">
-        <v>1.1724</v>
+        <v>1.128</v>
       </c>
       <c r="G13" t="n">
         <v>3.746</v>
@@ -1468,13 +1468,13 @@
         <v>2.0876</v>
       </c>
       <c r="S13" t="n">
-        <v>2.0436</v>
+        <v>0.5838</v>
       </c>
       <c r="T13" t="n">
-        <v>1.3135</v>
+        <v>-0.1019</v>
       </c>
       <c r="U13" t="n">
-        <v>0.7301</v>
+        <v>0.6858</v>
       </c>
       <c r="V13" t="n">
         <v>1.8608</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.7564</v>
+        <v>2.544</v>
       </c>
       <c r="E14" t="n">
         <v>2.2094</v>
       </c>
       <c r="F14" t="n">
-        <v>0.547</v>
+        <v>0.3345</v>
       </c>
       <c r="G14" t="n">
         <v>0.7123</v>
@@ -1546,13 +1546,13 @@
         <v>0.232</v>
       </c>
       <c r="S14" t="n">
-        <v>0.8817</v>
+        <v>0.6693</v>
       </c>
       <c r="T14" t="n">
         <v>0.5034</v>
       </c>
       <c r="U14" t="n">
-        <v>0.3782</v>
+        <v>0.1658</v>
       </c>
       <c r="V14" t="n">
         <v>0.9304</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>M. FAYE</t>
+          <t>S. HERRERA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.8397</v>
+        <v>2.4121</v>
       </c>
       <c r="E15" t="n">
-        <v>3.4655</v>
+        <v>3.4569</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.6258</v>
+        <v>-1.0448</v>
       </c>
       <c r="G15" t="n">
-        <v>1.6144</v>
+        <v>3.5663</v>
       </c>
       <c r="H15" t="n">
-        <v>1.2965</v>
+        <v>-0.1043</v>
       </c>
       <c r="I15" t="n">
-        <v>0.3179</v>
+        <v>3.6706</v>
       </c>
       <c r="J15" t="n">
-        <v>1.4716</v>
+        <v>4.1919</v>
       </c>
       <c r="K15" t="n">
-        <v>1.3612</v>
+        <v>0.6218</v>
       </c>
       <c r="L15" t="n">
-        <v>0.1104</v>
+        <v>3.5701</v>
       </c>
       <c r="M15" t="n">
-        <v>0.1428</v>
+        <v>-0.6256</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.06469999999999999</v>
+        <v>-0.7261</v>
       </c>
       <c r="O15" t="n">
-        <v>0.2075</v>
+        <v>0.1005</v>
       </c>
       <c r="P15" t="n">
-        <v>1.3917</v>
+        <v>1.8556</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.3917</v>
+        <v>1.8556</v>
       </c>
       <c r="S15" t="n">
-        <v>1.7976</v>
+        <v>-0.3293</v>
       </c>
       <c r="T15" t="n">
-        <v>1.8521</v>
+        <v>-0.735</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.0545</v>
+        <v>0.4057</v>
       </c>
       <c r="V15" t="n">
-        <v>-2.9641</v>
+        <v>-2.6805</v>
       </c>
       <c r="W15" t="n">
-        <v>0.1418</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-3.1058</v>
+        <v>-2.6805</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>S. HERRERA</t>
+          <t>Y. OUATTARA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.7165</v>
+        <v>0.6283</v>
       </c>
       <c r="E16" t="n">
-        <v>3.221</v>
+        <v>0.2902</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.5045</v>
+        <v>0.3382</v>
       </c>
       <c r="G16" t="n">
-        <v>3.5663</v>
+        <v>0.4603</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.1043</v>
+        <v>-0.3361</v>
       </c>
       <c r="I16" t="n">
-        <v>3.6706</v>
+        <v>0.7964</v>
       </c>
       <c r="J16" t="n">
-        <v>4.1919</v>
+        <v>0.5889</v>
       </c>
       <c r="K16" t="n">
-        <v>0.6218</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>3.5701</v>
+        <v>0.5889</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.6256</v>
+        <v>-0.1286</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.7261</v>
+        <v>-0.3361</v>
       </c>
       <c r="O16" t="n">
-        <v>0.1005</v>
+        <v>0.2075</v>
       </c>
       <c r="P16" t="n">
-        <v>1.8556</v>
+        <v>0.232</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.8556</v>
+        <v>0.232</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.0249</v>
+        <v>-0.0639</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.9709</v>
+        <v>-0.2987</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.054</v>
+        <v>0.2348</v>
       </c>
       <c r="V16" t="n">
-        <v>-2.6805</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-2.6805</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Y. OUATTARA</t>
+          <t>M. FAYE</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.5047</v>
+        <v>0.5258</v>
       </c>
       <c r="E17" t="n">
-        <v>0.2902</v>
+        <v>2.286</v>
       </c>
       <c r="F17" t="n">
-        <v>0.2145</v>
+        <v>-1.7602</v>
       </c>
       <c r="G17" t="n">
-        <v>0.4603</v>
+        <v>1.6144</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.3361</v>
+        <v>1.2965</v>
       </c>
       <c r="I17" t="n">
-        <v>0.7964</v>
+        <v>0.3179</v>
       </c>
       <c r="J17" t="n">
-        <v>0.5889</v>
+        <v>1.4716</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>1.3612</v>
       </c>
       <c r="L17" t="n">
-        <v>0.5889</v>
+        <v>0.1104</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.1286</v>
+        <v>0.1428</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.3361</v>
+        <v>-0.06469999999999999</v>
       </c>
       <c r="O17" t="n">
         <v>0.2075</v>
       </c>
       <c r="P17" t="n">
-        <v>0.232</v>
+        <v>1.3917</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>0.232</v>
+        <v>1.3917</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.1876</v>
+        <v>0.4837</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.2987</v>
+        <v>0.6726</v>
       </c>
       <c r="U17" t="n">
-        <v>0.1111</v>
+        <v>-0.1889</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>-2.9641</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>0.1418</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-3.1058</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.3814</v>
+        <v>-0.0682</v>
       </c>
       <c r="E18" t="n">
-        <v>1.521</v>
+        <v>0.8133</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.1396</v>
+        <v>-0.8815</v>
       </c>
       <c r="G18" t="n">
         <v>0.0998</v>
@@ -1858,13 +1858,13 @@
         <v>0.4639</v>
       </c>
       <c r="S18" t="n">
-        <v>0.6374</v>
+        <v>0.1878</v>
       </c>
       <c r="T18" t="n">
-        <v>1.1246</v>
+        <v>0.4169</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.4872</v>
+        <v>-0.2291</v>
       </c>
       <c r="V18" t="n">
         <v>-0.8197</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.0042</v>
+        <v>-0.1803</v>
       </c>
       <c r="E19" t="n">
-        <v>-3.0165</v>
+        <v>-2.8986</v>
       </c>
       <c r="F19" t="n">
-        <v>3.0207</v>
+        <v>2.7182</v>
       </c>
       <c r="G19" t="n">
         <v>-1.3352</v>
@@ -1936,13 +1936,13 @@
         <v>2.7834</v>
       </c>
       <c r="S19" t="n">
-        <v>0.8754999999999999</v>
+        <v>0.6909999999999999</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.0193</v>
+        <v>0.09859999999999999</v>
       </c>
       <c r="U19" t="n">
-        <v>0.8949</v>
+        <v>0.5924</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.6989</v>
+        <v>-0.2112</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.5458</v>
+        <v>0.5158</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.1531</v>
+        <v>-0.727</v>
       </c>
       <c r="G20" t="n">
         <v>-0.8168</v>
@@ -2014,13 +2014,13 @@
         <v>1.3917</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.1141</v>
+        <v>0.3736</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.3418</v>
+        <v>0.7198</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.7723</v>
+        <v>-0.3462</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.1024</v>
+        <v>-1.4569</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.8912</v>
+        <v>-0.5374</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.2112</v>
+        <v>-0.9195</v>
       </c>
       <c r="G21" t="n">
         <v>-1.0323</v>
@@ -2092,13 +2092,13 @@
         <v>2.0876</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.8381999999999999</v>
+        <v>-0.1926</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.0455</v>
+        <v>-0.6917</v>
       </c>
       <c r="U21" t="n">
-        <v>0.2074</v>
+        <v>0.4991</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.4209</v>
+        <v>-2.0613</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.7383</v>
+        <v>-3.5024</v>
       </c>
       <c r="F22" t="n">
-        <v>1.3174</v>
+        <v>1.4411</v>
       </c>
       <c r="G22" t="n">
         <v>-1.3391</v>
@@ -2170,13 +2170,13 @@
         <v>1.3917</v>
       </c>
       <c r="S22" t="n">
-        <v>0.351</v>
+        <v>0.7106</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.4323</v>
+        <v>-0.1964</v>
       </c>
       <c r="U22" t="n">
-        <v>0.7833</v>
+        <v>0.9069</v>
       </c>
       <c r="V22" t="n">
         <v>-0.5051</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.8988</v>
+        <v>-2.2532</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.6162</v>
+        <v>-2.2623</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.2825</v>
+        <v>0.0091</v>
       </c>
       <c r="G23" t="n">
         <v>-4.0817</v>
@@ -2248,13 +2248,13 @@
         <v>1.1598</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.1186</v>
+        <v>0.5269</v>
       </c>
       <c r="T23" t="n">
-        <v>0.4446</v>
+        <v>0.7984</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.5632</v>
+        <v>-0.2715</v>
       </c>
       <c r="V23" t="n">
         <v>0.1418</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-6.6813</v>
+        <v>-5.446</v>
       </c>
       <c r="E24" t="n">
-        <v>-6.2627</v>
+        <v>-5.3191</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.4186</v>
+        <v>-0.127</v>
       </c>
       <c r="G24" t="n">
         <v>-4.3641</v>
@@ -2326,13 +2326,13 @@
         <v>1.1598</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.905</v>
+        <v>0.3304</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.4165</v>
+        <v>0.5272</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.4885</v>
+        <v>-0.1968</v>
       </c>
       <c r="V24" t="n">
         <v>-0.2525</v>
@@ -2359,16 +2359,16 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.02109999999999701</v>
+        <v>1.551600000000002</v>
       </c>
       <c r="E25" t="n">
-        <v>1.042299999999999</v>
+        <v>1.0422</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.0633</v>
+        <v>0.5091</v>
       </c>
       <c r="G25" t="n">
-        <v>-2.770100000000001</v>
+        <v>-2.770099999999999</v>
       </c>
       <c r="H25" t="n">
         <v>-6.183</v>
@@ -2404,13 +2404,13 @@
         <v>16.2368</v>
       </c>
       <c r="S25" t="n">
-        <v>2.398400000000001</v>
+        <v>3.9713</v>
       </c>
       <c r="T25" t="n">
         <v>1.7132</v>
       </c>
       <c r="U25" t="n">
-        <v>0.6853</v>
+        <v>2.258</v>
       </c>
       <c r="V25" t="n">
         <v>-4.288900000000001</v>
